--- a/BVSimulationFiles/85.xlsx
+++ b/BVSimulationFiles/85.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.003702830188679245</v>
+        <v>0.00740566037735849</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003750217586934745</v>
+        <v>0.00750043517386949</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003795556998614881</v>
+        <v>0.007591113997229762</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003838896414960655</v>
+        <v>0.00767779282992131</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00388028288576378</v>
+        <v>0.00776056577152756</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003919762536308411</v>
+        <v>0.007839525072616822</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003957380584023208</v>
+        <v>0.007914761168046416</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003993181354848496</v>
+        <v>0.007986362709696992</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004027208299323292</v>
+        <v>0.008054416598646584</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004059504008396758</v>
+        <v>0.008119008016793517</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004090110228968709</v>
+        <v>0.008180220457937417</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004119067879163604</v>
+        <v>0.008238135758327207</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004146417063342483</v>
+        <v>0.008292834126684965</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004172197086857147</v>
+        <v>0.008344394173714294</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004196446470550896</v>
+        <v>0.008392892941101793</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.004219202965009994</v>
+        <v>0.008438405930019988</v>
       </c>
       <c r="R2" t="n">
-        <v>0.004240503564570009</v>
+        <v>0.008481007129140019</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004260384521081103</v>
+        <v>0.008520769042162205</v>
       </c>
       <c r="T2" t="n">
-        <v>0.004278881357436266</v>
+        <v>0.008557762714872533</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004296028880866426</v>
+        <v>0.008592057761732852</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.003702830188679245</v>
+        <v>0.00740566037735849</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003750217586934745</v>
+        <v>0.00750043517386949</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003795556998614881</v>
+        <v>0.007591113997229762</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003838896414960655</v>
+        <v>0.00767779282992131</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00388028288576378</v>
+        <v>0.00776056577152756</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003919762536308411</v>
+        <v>0.007839525072616822</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003957380584023208</v>
+        <v>0.007914761168046416</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003993181354848496</v>
+        <v>0.007986362709696992</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004027208299323292</v>
+        <v>0.008054416598646584</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004059504008396758</v>
+        <v>0.008119008016793517</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004090110228968709</v>
+        <v>0.008180220457937417</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004119067879163604</v>
+        <v>0.008238135758327207</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004146417063342483</v>
+        <v>0.008292834126684965</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004172197086857147</v>
+        <v>0.008344394173714294</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004196446470550896</v>
+        <v>0.008392892941101793</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004219202965009994</v>
+        <v>0.008438405930019988</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004240503564570009</v>
+        <v>0.008481007129140019</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004260384521081103</v>
+        <v>0.008520769042162205</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004278881357436266</v>
+        <v>0.008557762714872533</v>
       </c>
       <c r="U3" t="n">
-        <v>0.004296028880866426</v>
+        <v>0.008592057761732852</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/85.xlsx
+++ b/BVSimulationFiles/85.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00740566037735849</v>
+        <v>0.07405660377358489</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00750043517386949</v>
+        <v>0.07500435173869489</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007591113997229762</v>
+        <v>0.07591113997229762</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00767779282992131</v>
+        <v>0.07677792829921309</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00776056577152756</v>
+        <v>0.0776056577152756</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007839525072616822</v>
+        <v>0.07839525072616822</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007914761168046416</v>
+        <v>0.07914761168046416</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007986362709696992</v>
+        <v>0.07986362709696992</v>
       </c>
       <c r="J2" t="n">
-        <v>0.008054416598646584</v>
+        <v>0.08054416598646584</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008119008016793517</v>
+        <v>0.08119008016793516</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008180220457937417</v>
+        <v>0.08180220457937418</v>
       </c>
       <c r="M2" t="n">
-        <v>0.008238135758327207</v>
+        <v>0.08238135758327207</v>
       </c>
       <c r="N2" t="n">
-        <v>0.008292834126684965</v>
+        <v>0.08292834126684966</v>
       </c>
       <c r="O2" t="n">
-        <v>0.008344394173714294</v>
+        <v>0.08344394173714295</v>
       </c>
       <c r="P2" t="n">
-        <v>0.008392892941101793</v>
+        <v>0.08392892941101793</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.008438405930019988</v>
+        <v>0.08438405930019988</v>
       </c>
       <c r="R2" t="n">
-        <v>0.008481007129140019</v>
+        <v>0.08481007129140018</v>
       </c>
       <c r="S2" t="n">
-        <v>0.008520769042162205</v>
+        <v>0.08520769042162205</v>
       </c>
       <c r="T2" t="n">
-        <v>0.008557762714872533</v>
+        <v>0.08557762714872533</v>
       </c>
       <c r="U2" t="n">
-        <v>0.008592057761732852</v>
+        <v>0.08592057761732852</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.00740566037735849</v>
+        <v>0.07405660377358489</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00750043517386949</v>
+        <v>0.07500435173869489</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007591113997229762</v>
+        <v>0.07591113997229762</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00767779282992131</v>
+        <v>0.07677792829921309</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00776056577152756</v>
+        <v>0.0776056577152756</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007839525072616822</v>
+        <v>0.07839525072616822</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007914761168046416</v>
+        <v>0.07914761168046416</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007986362709696992</v>
+        <v>0.07986362709696992</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008054416598646584</v>
+        <v>0.08054416598646584</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008119008016793517</v>
+        <v>0.08119008016793516</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008180220457937417</v>
+        <v>0.08180220457937418</v>
       </c>
       <c r="M3" t="n">
-        <v>0.008238135758327207</v>
+        <v>0.08238135758327207</v>
       </c>
       <c r="N3" t="n">
-        <v>0.008292834126684965</v>
+        <v>0.08292834126684966</v>
       </c>
       <c r="O3" t="n">
-        <v>0.008344394173714294</v>
+        <v>0.08344394173714295</v>
       </c>
       <c r="P3" t="n">
-        <v>0.008392892941101793</v>
+        <v>0.08392892941101793</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.008438405930019988</v>
+        <v>0.08438405930019988</v>
       </c>
       <c r="R3" t="n">
-        <v>0.008481007129140019</v>
+        <v>0.08481007129140018</v>
       </c>
       <c r="S3" t="n">
-        <v>0.008520769042162205</v>
+        <v>0.08520769042162205</v>
       </c>
       <c r="T3" t="n">
-        <v>0.008557762714872533</v>
+        <v>0.08557762714872533</v>
       </c>
       <c r="U3" t="n">
-        <v>0.008592057761732852</v>
+        <v>0.08592057761732852</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/85.xlsx
+++ b/BVSimulationFiles/85.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -421,60 +421,90 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.009167894736842106</v>
+        <v>0.006006551724137931</v>
       </c>
       <c r="D1" t="n">
-        <v>0.01833578947368421</v>
+        <v>0.01201310344827586</v>
       </c>
       <c r="E1" t="n">
-        <v>0.02750368421052632</v>
+        <v>0.01801965517241379</v>
       </c>
       <c r="F1" t="n">
-        <v>0.03667157894736842</v>
+        <v>0.02402620689655172</v>
       </c>
       <c r="G1" t="n">
-        <v>0.04583947368421053</v>
+        <v>0.03003275862068966</v>
       </c>
       <c r="H1" t="n">
-        <v>0.05500736842105264</v>
+        <v>0.03603931034482758</v>
       </c>
       <c r="I1" t="n">
-        <v>0.06417526315789474</v>
+        <v>0.04204586206896552</v>
       </c>
       <c r="J1" t="n">
-        <v>0.07334315789473685</v>
+        <v>0.04805241379310345</v>
       </c>
       <c r="K1" t="n">
-        <v>0.08251105263157896</v>
+        <v>0.05405896551724138</v>
       </c>
       <c r="L1" t="n">
-        <v>0.09167894736842105</v>
+        <v>0.06006551724137931</v>
       </c>
       <c r="M1" t="n">
-        <v>0.1008468421052632</v>
+        <v>0.06607206896551725</v>
       </c>
       <c r="N1" t="n">
-        <v>0.1100147368421053</v>
+        <v>0.07207862068965516</v>
       </c>
       <c r="O1" t="n">
-        <v>0.1191826315789474</v>
+        <v>0.07808517241379309</v>
       </c>
       <c r="P1" t="n">
-        <v>0.1283505263157895</v>
+        <v>0.08409172413793103</v>
       </c>
       <c r="Q1" t="n">
-        <v>0.1375184210526316</v>
+        <v>0.09009827586206896</v>
       </c>
       <c r="R1" t="n">
-        <v>0.1466863157894737</v>
+        <v>0.09610482758620689</v>
       </c>
       <c r="S1" t="n">
-        <v>0.1558542105263158</v>
+        <v>0.1021113793103448</v>
       </c>
       <c r="T1" t="n">
-        <v>0.1650221052631579</v>
+        <v>0.1081179310344828</v>
       </c>
       <c r="U1" t="n">
+        <v>0.1141244827586207</v>
+      </c>
+      <c r="V1" t="n">
+        <v>0.1201310344827586</v>
+      </c>
+      <c r="W1" t="n">
+        <v>0.1261375862068966</v>
+      </c>
+      <c r="X1" t="n">
+        <v>0.1321441379310345</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>0.1381506896551724</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>0.1441572413793103</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>0.1501637931034483</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>0.1561703448275862</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>0.1621768965517242</v>
+      </c>
+      <c r="AD1" t="n">
+        <v>0.1681834482758621</v>
+      </c>
+      <c r="AE1" t="n">
         <v>0.17419</v>
       </c>
     </row>
@@ -483,64 +513,94 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.07405660377358489</v>
+        <v>0.5559657810926388</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07500435173869489</v>
+        <v>0.5555159291515046</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07591113997229762</v>
+        <v>0.5548968501436302</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07677792829921309</v>
+        <v>0.5541148793776306</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0776056577152756</v>
+        <v>0.5531761771276003</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07839525072616822</v>
+        <v>0.552086732914726</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07914761168046416</v>
+        <v>0.5508523696908656</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07986362709696992</v>
+        <v>0.5494787479262441</v>
       </c>
       <c r="J2" t="n">
-        <v>0.08054416598646584</v>
+        <v>0.5479713696033774</v>
       </c>
       <c r="K2" t="n">
-        <v>0.08119008016793516</v>
+        <v>0.5463355821192825</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08180220457937418</v>
+        <v>0.5445765820979936</v>
       </c>
       <c r="M2" t="n">
-        <v>0.08238135758327207</v>
+        <v>0.5426994191153627</v>
       </c>
       <c r="N2" t="n">
-        <v>0.08292834126684966</v>
+        <v>0.5407089993380702</v>
       </c>
       <c r="O2" t="n">
-        <v>0.08344394173714295</v>
+        <v>0.538610089078743</v>
       </c>
       <c r="P2" t="n">
-        <v>0.08392892941101793</v>
+        <v>0.5364073182690303</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.08438405930019988</v>
+        <v>0.5341051838524448</v>
       </c>
       <c r="R2" t="n">
-        <v>0.08481007129140018</v>
+        <v>0.5317080530987464</v>
       </c>
       <c r="S2" t="n">
-        <v>0.08520769042162205</v>
+        <v>0.5292201668415997</v>
       </c>
       <c r="T2" t="n">
-        <v>0.08557762714872533</v>
+        <v>0.5266456426412039</v>
       </c>
       <c r="U2" t="n">
-        <v>0.08592057761732852</v>
+        <v>0.523988477873558</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.5212525527479803</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.5184416332544826</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.5155593740425441</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.5126093212328171</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.5095949151632486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.5065194930710798</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.5033862917121458</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.5001984499188759</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.4969590110983557</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.493670925671794</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +608,94 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.07405660377358489</v>
+        <v>0.5559657810926388</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07500435173869489</v>
+        <v>0.5555159291515046</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07591113997229762</v>
+        <v>0.5548968501436302</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07677792829921309</v>
+        <v>0.5541148793776306</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0776056577152756</v>
+        <v>0.5531761771276003</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07839525072616822</v>
+        <v>0.552086732914726</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07914761168046416</v>
+        <v>0.5508523696908656</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07986362709696992</v>
+        <v>0.5494787479262441</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08054416598646584</v>
+        <v>0.5479713696033774</v>
       </c>
       <c r="K3" t="n">
-        <v>0.08119008016793516</v>
+        <v>0.5463355821192825</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08180220457937418</v>
+        <v>0.5445765820979936</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08238135758327207</v>
+        <v>0.5426994191153627</v>
       </c>
       <c r="N3" t="n">
-        <v>0.08292834126684966</v>
+        <v>0.5407089993380702</v>
       </c>
       <c r="O3" t="n">
-        <v>0.08344394173714295</v>
+        <v>0.538610089078743</v>
       </c>
       <c r="P3" t="n">
-        <v>0.08392892941101793</v>
+        <v>0.5364073182690303</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.08438405930019988</v>
+        <v>0.5341051838524448</v>
       </c>
       <c r="R3" t="n">
-        <v>0.08481007129140018</v>
+        <v>0.5317080530987464</v>
       </c>
       <c r="S3" t="n">
-        <v>0.08520769042162205</v>
+        <v>0.5292201668415997</v>
       </c>
       <c r="T3" t="n">
-        <v>0.08557762714872533</v>
+        <v>0.5266456426412039</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08592057761732852</v>
+        <v>0.523988477873558</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.5212525527479803</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.5184416332544826</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.5155593740425441</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.5126093212328171</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.5095949151632486</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.5065194930710798</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.5033862917121458</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5001984499188759</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.4969590110983557</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.493670925671794</v>
       </c>
     </row>
   </sheetData>
